--- a/templates/Campus Contacts.template.xlsx
+++ b/templates/Campus Contacts.template.xlsx
@@ -484,16 +484,8 @@
           <t>Doctor</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>9876543211</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>9876543212</t>
-        </is>
-      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
     </row>
   </sheetData>

--- a/templates/Campus Contacts.template.xlsx
+++ b/templates/Campus Contacts.template.xlsx
@@ -433,13 +433,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,6 +464,11 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -477,6 +483,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -487,6 +494,26 @@
       <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A Cab</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>9876543211</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7 AM - 11 PM, daily</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
